--- a/backend/exports/NGP3069047.xlsx
+++ b/backend/exports/NGP3069047.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gihub\logix\backend\exports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F680FDF6-D65F-496B-8C0B-5FD1CA97B890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C6417CF-D8FB-441D-931B-81A6E779EA2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="dropdown_items_sheet" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet1!$A$1:$GN$50</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -1127,12 +1130,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1149,7 +1158,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1168,7 +1177,13 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1528,7 +1543,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:196" s="4" customFormat="1" ht="85.5" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>164</v>
       </c>
       <c r="B1" s="4" t="s">
@@ -1648,7 +1663,7 @@
       <c r="AN1" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="AO1" s="4" t="s">
+      <c r="AO1" s="6" t="s">
         <v>204</v>
       </c>
       <c r="AP1" s="4" t="s">
@@ -1750,88 +1765,88 @@
       <c r="BV1" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="BW1" s="4" t="s">
+      <c r="BW1" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="BX1" s="4" t="s">
+      <c r="BX1" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="BY1" s="4" t="s">
+      <c r="BY1" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="BZ1" s="4" t="s">
+      <c r="BZ1" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="CA1" s="4" t="s">
+      <c r="CA1" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="CB1" s="4" t="s">
+      <c r="CB1" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="CC1" s="4" t="s">
+      <c r="CC1" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="CD1" s="4" t="s">
+      <c r="CD1" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="CE1" s="5" t="s">
+      <c r="CE1" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="CF1" s="5" t="s">
+      <c r="CF1" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="CG1" s="5" t="s">
+      <c r="CG1" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="CH1" s="5" t="s">
+      <c r="CH1" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="CI1" s="5" t="s">
+      <c r="CI1" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="CJ1" s="5" t="s">
+      <c r="CJ1" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="CK1" s="5" t="s">
+      <c r="CK1" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="CL1" s="5" t="s">
+      <c r="CL1" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="CM1" s="5" t="s">
+      <c r="CM1" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="CN1" s="5" t="s">
+      <c r="CN1" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="CO1" s="5" t="s">
+      <c r="CO1" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="CP1" s="4" t="s">
+      <c r="CP1" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="CQ1" s="4" t="s">
+      <c r="CQ1" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="CR1" s="4" t="s">
+      <c r="CR1" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="CS1" s="4" t="s">
+      <c r="CS1" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="CT1" s="5" t="s">
+      <c r="CT1" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="CU1" s="6" t="s">
+      <c r="CU1" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="CV1" s="6" t="s">
+      <c r="CV1" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="CW1" s="5" t="s">
+      <c r="CW1" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="CX1" s="5" t="s">
+      <c r="CX1" s="7" t="s">
         <v>265</v>
       </c>
       <c r="CY1" s="4" t="s">
@@ -1918,88 +1933,88 @@
       <c r="DZ1" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="EA1" s="4" t="s">
+      <c r="EA1" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="EB1" s="4" t="s">
+      <c r="EB1" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="EC1" s="4" t="s">
+      <c r="EC1" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="ED1" s="4" t="s">
+      <c r="ED1" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="EE1" s="4" t="s">
+      <c r="EE1" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="EF1" s="4" t="s">
+      <c r="EF1" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="EG1" s="4" t="s">
+      <c r="EG1" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="EH1" s="4" t="s">
+      <c r="EH1" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="EI1" s="4" t="s">
+      <c r="EI1" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="EJ1" s="4" t="s">
+      <c r="EJ1" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="EK1" s="4" t="s">
+      <c r="EK1" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="EL1" s="4" t="s">
+      <c r="EL1" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="EM1" s="4" t="s">
+      <c r="EM1" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="EN1" s="5" t="s">
+      <c r="EN1" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="EO1" s="4" t="s">
+      <c r="EO1" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="EP1" s="4" t="s">
+      <c r="EP1" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="EQ1" s="4" t="s">
+      <c r="EQ1" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="ER1" s="4" t="s">
+      <c r="ER1" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="ES1" s="4" t="s">
+      <c r="ES1" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="ET1" s="4" t="s">
+      <c r="ET1" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="EU1" s="4" t="s">
+      <c r="EU1" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="EV1" s="4" t="s">
+      <c r="EV1" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="EW1" s="4" t="s">
+      <c r="EW1" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="EX1" s="4" t="s">
+      <c r="EX1" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="EY1" s="4" t="s">
+      <c r="EY1" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="EZ1" s="4" t="s">
+      <c r="EZ1" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="FA1" s="4" t="s">
+      <c r="FA1" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="FB1" s="4" t="s">
+      <c r="FB1" s="6" t="s">
         <v>320</v>
       </c>
       <c r="FC1" s="4" t="s">
@@ -16853,6 +16868,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:GN50" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
